--- a/design/tables/TechnologyEffect.xlsx
+++ b/design/tables/TechnologyEffect.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TechnologyEffect" sheetId="1" r:id="Rce5e91c7a5734f2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TechnologyEffect" sheetId="1" r:id="R3775ff28ced540bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -650,6 +650,86 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>bossDamage</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>global</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>bossDamage</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>add</x:v>
+      </x:c>
+      <x:c r="F20" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>obstacleDamage</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>global</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>obstacleDamage</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>add</x:v>
+      </x:c>
+      <x:c r="F21" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>obstacleReward</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>global</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>obstacleReward</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>add</x:v>
+      </x:c>
+      <x:c r="F22" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>challengeXp</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>global</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>challengeXp</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>add</x:v>
+      </x:c>
+      <x:c r="F23" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
